--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_460_Malaysia_Peninsula_East.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_460_Malaysia_Peninsula_East.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re697e980695b40d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rbd46f4712dfe47d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R6e426a68b82c46f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R05c12ff71ac44af8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R43f70a754a43478c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3a278f0202ec401b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb2bb062d413b4188"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Ra38ccfd615f44c2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re27719b793f14319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rea0f49b961394137"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R2e3d6d5161e94856"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R088ae01047dc47ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ460CommercialTable" displayName="EEZ460CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ460CommercialTable" displayName="EEZ460CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ460FunctionalTable" displayName="EEZ460FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ460FunctionalTable" displayName="EEZ460FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ460ValidationTable" displayName="EEZ460ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ460ValidationTable" displayName="EEZ460ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -11213,7 +11167,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4f14259b1ad4474"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4865d057d4314521"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11223,20 +11177,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11244,606 +11188,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>18738.5073433504</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.4342736437850108</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>271.8151404238601</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>18738.5073433504</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>272.6013668638015</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$158,A2,'Species'!$U$2:$U$158))</x:f>
-        <x:v>5108142.714784701</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.4342736437850108</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>271.8151404238601</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>5093410.0048663225</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>14732.709918378852</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.002892504217077</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0028925042170771633</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>14152.839644279702</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.9726057131647483</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>93.88705426788984</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>14152.839644279702</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>179.8347198709748</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$158,A3,'Species'!$U$2:$U$158))</x:f>
-        <x:v>2545171.952807867</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.9726057131647483</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>93.88705426788984</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1328768.423727231</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1216403.5290806359</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.915436811531532</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.9154368115315318</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2742.5318918064995</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.6352391279386467</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>431.75674201858703</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2742.5318918064995</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>510.3653396735814</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$158,A4,'Species'!$U$2:$U$158))</x:f>
-        <x:v>1399693.2205274538</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.6352391279386467</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>431.75674201858703</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1184106.6344884462</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>215586.58603900764</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1820668677632606</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.18206686776326073</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>32948.735347360096</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.0333451159140346</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>107.98044574514212</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>32948.735347360096</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>325.3742071282332</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$158,A5,'Species'!$U$2:$U$158))</x:f>
-        <x:v>10720668.639525283</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.0333451159140346</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>107.98044574514212</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3557819.1295466633</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>7162849.50997862</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>3.013269716409476</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>2.0132697164094764</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>652.9632883130001</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.090760403965838</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.324247289277562</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>652.9632883130001</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.350017497145966</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$158,A6,'Species'!$U$2:$U$158))</x:f>
-        <x:v>8064.108035659518</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.090760403965838</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.324247289277562</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>8047.281035989255</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>16.82699967026292</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0020910167788362</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0020910167788360796</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>101889.59135941452</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.597737407340766</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>396.03850035838315</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>101889.59135941452</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>701.7856826912848</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$158,A7,'Species'!$U$2:$U$158))</x:f>
-        <x:v>71504656.43130276</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.597737407340766</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>396.03850035838315</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>40352200.964111</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>31152455.467191756</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7720137866803984</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7720137866803983</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>301318.95078837406</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6382595024603477</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>434.7699331274051</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>301318.95078837406</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>643.271776338047</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$158,A8,'Species'!$U$2:$U$158))</x:f>
-        <x:v>193829976.71795392</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6382595024603477</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>434.7699331274051</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>131004420.08428127</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>62825556.633672655</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4795682206238083</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4795682206238083</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1307.1795176977998</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.908719991546001</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>810.4383646712112</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1307.1795176977998</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>810.6501127612592</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$158,A9,'Species'!$U$2:$U$158))</x:f>
-        <x:v>1059665.2234209299</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.908719991546001</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>810.4383646712112</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1059388.4306547074</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>276.79276622249745</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0002612759949165</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0002612759949166503</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>10507.836627384699</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.000025221130852</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1000.0580754862445</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>10507.836627384699</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1114.3954185759246</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$158,A10,'Species'!$U$2:$U$158))</x:f>
-        <x:v>11709884.996701803</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.000025221130852</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1000.0580754862445</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>10508446.875106212</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1201438.1215955913</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1143307032784946</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.11433070327849452</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>9230.398757401501</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.483275413354369</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>3042.814053080401</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>9230.398757401501</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>3056.5484569087507</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$158,A11,'Species'!$U$2:$U$158))</x:f>
-        <x:v>28213161.07858801</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.483275413354369</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>3042.814053080401</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>28086387.05455716</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>126774.02403084934</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.004513717758877</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.004513717758877057</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea659b9fcccf46d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb2e2881e3cd44bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11853,20 +11403,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11874,1146 +11414,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>17059.0556840509</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6912227206928723</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>491.1596946468925</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>17059.0556840509</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>491.9255957339512</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$158,A2,'Species'!$U$2:$U$158))</x:f>
-        <x:v>8391786.130035385</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6912227206928723</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>491.1596946468925</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>8378720.580742776</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>13065.549292609096</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0015593728382157</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0015593728382156922</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>6441.3756836849</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4600000000000004</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266084</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>6441.3756836849</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$158,A3,'Species'!$U$2:$U$158))</x:f>
-        <x:v>1857713.0395220928</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4600000000000004</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266084</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1857713.0395220947</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>-1.862645149230957e-9</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>-1.0026549362597633e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7525.6168743616</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.419513929099428</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2627.3257911713376</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7525.6168743616</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2627.958327030852</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$158,A4,'Species'!$U$2:$U$158))</x:f>
-        <x:v>19777007.53102246</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.419513929099428</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2627.3257911713376</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>19772247.30848446</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4760.22253799811</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.000240752731024</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0002407527310239263</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>789.4932266281</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.0783523241801625</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1197.7117886446608</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>789.4932266281</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1295.738538959777</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$158,A5,'Species'!$U$2:$U$158))</x:f>
-        <x:v>1022976.7999897345</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.0783523241801625</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1197.7117886446608</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>945585.3445875862</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>77391.4554021483</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0818450241907063</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.08184502419070626</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>23150.4103931454</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.3789318948084555</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2392.9404708444918</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>23150.4103931454</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2497.2978639360445</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$158,A6,'Species'!$U$2:$U$158))</x:f>
-        <x:v>57813470.42404482</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.3789318948084555</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2392.9404708444918</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>55397553.94641657</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2415916.477628246</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0436105261969697</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.04361052619696977</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6644.9710580396995</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.849943933321011</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>707.8543956865993</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6644.9710580396995</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>707.8668000946773</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$158,A7,'Species'!$U$2:$U$158))</x:f>
-        <x:v>4703754.3995763045</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.849943933321011</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>707.8543956865993</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>4703671.972643634</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>82.42693267017603</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0000175239542957</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.000017523954295615794</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3041.8088874371997</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6610421962288</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>458.18640212943365</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3041.8088874371997</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>546.5346070676928</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$158,A8,'Species'!$U$2:$U$158))</x:f>
-        <x:v>1662453.8250705057</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6610421962288</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>458.18640212943365</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1393715.4701001858</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>268738.3549703199</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1928215340474064</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.19282153404740632</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3862.865569345</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.258197760647629</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1812.165093569173</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3862.865569345</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1813.713283921884</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$158,A9,'Species'!$U$2:$U$158))</x:f>
-        <x:v>7006130.597125499</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.258197760647629</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1812.165093569173</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>7000150.145917219</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>5980.451208279468</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0008543318476915</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0008543318476915124</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>3192.9823745728004</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.5156926994589606</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>32.78632197091514</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>3192.9823745728004</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>35.63405963009521</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$158,A10,'Species'!$U$2:$U$158))</x:f>
-        <x:v>113778.92433337017</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.5156926994589606</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>32.78632197091514</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>104686.148180201</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>9092.77615316918</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.086857490806877</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.08685749080687707</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>5509.8521151502</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.5874850146694737</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>386.79870791388186</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>5509.8521151502</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>448.5523166916654</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$158,A11,'Species'!$U$2:$U$158))</x:f>
-        <x:v>2471456.930879095</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.5874850146694737</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>386.79870791388186</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2131203.6789366663</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>340253.25194242876</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1596530896156267</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.15965308961562663</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>89383.586472884</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.594269742954615</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>392.8888853181089</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>89383.586472884</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>742.512391903098</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$158,A12,'Species'!$U$2:$U$158))</x:f>
-        <x:v>66368420.58885849</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.594269742954615</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>392.8888853181089</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>35117817.65506619</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>31250602.9337923</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.8898788427214241</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.8898788427214241</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>122585.13128197845</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.6222629092925436</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>419.04716735866884</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>122585.13128197845</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>614.2508208191333</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$158,A13,'Species'!$U$2:$U$158))</x:f>
-        <x:v>75298017.51017648</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.6222629092925436</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>419.04716735866884</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>51368952.02400362</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>23929065.486172862</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.4658274024159832</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.4658274024159831</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>57467.376972075304</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.601181039777794</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>399.1912743553326</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>57467.376972075304</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>537.6990439761194</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$158,A14,'Species'!$U$2:$U$158))</x:f>
-        <x:v>30900153.657700147</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.601181039777794</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>399.1912743553326</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>22940475.447341036</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>7959678.210359111</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.3469709347842524</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.34697093478425245</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>665.2266555862001</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.095766033879335</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>12.467116961665562</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>665.2266555862001</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>12.551674174270957</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$158,A15,'Species'!$U$2:$U$158))</x:f>
-        <x:v>8349.708232957948</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.095766033879335</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>12.467116961665562</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>8293.45852121077</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>56.24971174717757</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0067824191322978</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.0067824191322977305</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>10959.8572697069</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.105720147374396</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>127.5616556400033</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>10959.8572697069</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>221.84531866075292</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$158,A16,'Species'!$U$2:$U$158))</x:f>
-        <x:v>2431393.0284744967</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.105720147374396</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>127.5616556400033</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1398057.5389019381</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1033335.4895725586</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.739122289905293</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.7391222899052928</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>10784.601701732</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.2270442282152176</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>168.67247913947088</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>10784.601701732</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>169.36985136119503</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$158,A17,'Species'!$U$2:$U$158))</x:f>
-        <x:v>1826586.3872120397</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.2270442282152176</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>168.67247913947088</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>1819065.5055628929</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>7520.881649146788</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0041344754359571</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.004134475435957168</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>35706.654043136296</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.721530848724235</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>526.6606232239632</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>35706.654043136296</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>529.2609589680027</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$158,A18,'Species'!$U$2:$U$158))</x:f>
-        <x:v>18898137.960409027</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.721530848724235</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>526.6606232239632</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>18805288.671600606</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>92849.2888084203</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0049374030056044</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.004937403005604458</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>61725.01615310909</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.258405690556726</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>181.30329230156153</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>61725.01615310909</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>288.4578583528881</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$158,A19,'Species'!$U$2:$U$158))</x:f>
-        <x:v>17805065.96632327</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.258405690556726</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>181.30329230156153</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>11190948.645925745</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>6614117.320397526</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.5910238291376226</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.5910238291376225</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>24251.120256951803</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.2382690179094267</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>173.08882027630074</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>24251.120256951803</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>261.5441425769402</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$158,A20,'Species'!$U$2:$U$158))</x:f>
-        <x:v>6342738.454134725</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.2382690179094267</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>173.08882027630074</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>4197597.795654487</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>2145140.658480238</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.5110400669404223</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.5110400669404224</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>2742.5318918064995</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.6352391279386467</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>431.75674201858703</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>2742.5318918064995</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>510.3653396735814</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$158,A21,'Species'!$U$2:$U$158))</x:f>
-        <x:v>1399693.2205274538</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.6352391279386467</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>431.75674201858703</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1184106.6344884462</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>215586.58603900764</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.1820668677632606</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.18206686776326073</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re51eadb98cba4295"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd03b46b09ff64130"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13188,7 +11984,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -13287,7 +12083,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>326099085.08364826</x:v>
+        <x:v>222182994.882375</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13301,7 +12097,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>326099085.0836483</x:v>
+        <x:v>249715851.01259753</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13315,7 +12111,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-103916090.20127338</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13329,7 +12125,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-76383234.07105085</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13340,9 +12136,9 @@
         <x:v>EEZ_460</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13354,47 +12150,19 @@
         <x:v>EEZ_460</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_460</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_460</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8a4a2bf82aa401d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a70752824264496"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13441,7 +12209,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
